--- a/public/upload/report/REKAP RAPOR YAYASAN PENDIDIKAN ALQALAM KENDARI BULAN 09 TAHUN 2026 .xlsx
+++ b/public/upload/report/REKAP RAPOR YAYASAN PENDIDIKAN ALQALAM KENDARI BULAN 09 TAHUN 2026 .xlsx
@@ -917,7 +917,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="4">
-        <v>7.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -950,7 +950,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="4">
-        <v>12.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8">
